--- a/Listado_ Definitivo_Sorteo_Empleados.xlsx
+++ b/Listado_ Definitivo_Sorteo_Empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sm68099\PYTHON\Bolillero_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4936BE1C-419E-4081-9BFA-50A82BD559CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582754AB-F41D-4ED8-804C-4CDCF8A898F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B455F77-704B-4AAD-B4EC-346F0192F815}"/>
   </bookViews>
@@ -155,88 +155,88 @@
     <t>Sergio Roldan</t>
   </si>
   <si>
-    <t>Pc - HP ProDesk 400</t>
-  </si>
-  <si>
-    <t>Pc - HP Compaq 6300pro - 1</t>
-  </si>
-  <si>
-    <t>Pc - HP Compaq 6300pro - 3</t>
-  </si>
-  <si>
-    <t>Notebook - HP EliteBook 6930P</t>
-  </si>
-  <si>
-    <t>Notebook - HP EliteBook 8440P - 1</t>
-  </si>
-  <si>
-    <t>Notebook - HP EliteBook 8440P - 2</t>
-  </si>
-  <si>
-    <t>Notebook - HP EliteBook 8470P</t>
-  </si>
-  <si>
-    <t>Pc - HP Compaq 6300pro - 2</t>
-  </si>
-  <si>
-    <t>Pc - Lenovo Think Centre</t>
-  </si>
-  <si>
-    <t>Pc - HP Compaq dc5200</t>
-  </si>
-  <si>
-    <t>HP EliteBook 840 G3 - 1</t>
-  </si>
-  <si>
-    <t>HP EliteBook 840 G3 - 2</t>
-  </si>
-  <si>
-    <t>HP EliteBook 840 G3 - 3</t>
-  </si>
-  <si>
-    <t>Mobiliario - Silla Oficina - 1</t>
-  </si>
-  <si>
-    <t>Mobiliario - Silla Oficina - 2</t>
-  </si>
-  <si>
-    <t>Mobiliario - Silla Oficina - 3</t>
-  </si>
-  <si>
-    <t>Mobiliario - Sillón - 1</t>
-  </si>
-  <si>
-    <t>Mobiliario - Sillón - 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobiliario - Mesa Trabajo - 1 </t>
-  </si>
-  <si>
-    <t>Mobiliario - Mesa Trabajo - 2</t>
-  </si>
-  <si>
-    <t>Mobiliario - Armario Bajo - 1</t>
-  </si>
-  <si>
-    <t>Mobiliario - Armario alto - 1</t>
-  </si>
-  <si>
-    <t>Mobiliario - Armario alto - 2</t>
-  </si>
-  <si>
-    <t>Impresora - Ricoh Aficio MP C300</t>
-  </si>
-  <si>
-    <t>Impresora - Ricoh Aficio SP C430dn</t>
-  </si>
-  <si>
-    <t>Impresora - Ricoh Aficio 4310N</t>
-  </si>
-  <si>
-    <t>Impresora - HP Laserjet Pro MFP 479fdw</t>
-  </si>
-  <si>
-    <t>Impresora - HP Laserjet 1022</t>
+    <t>Mobiliario-armario_alto-2</t>
+  </si>
+  <si>
+    <t>Mobiliario-armario_bajo-1</t>
+  </si>
+  <si>
+    <t>Mobiliario-mesa_trabajo-2</t>
+  </si>
+  <si>
+    <t>Mobiliario-armario_alto-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobiliario-mesa_trabajo-1 </t>
+  </si>
+  <si>
+    <t>Mobiliario-silla_oficina-3</t>
+  </si>
+  <si>
+    <t>Mobiliario-sillón_oficina-2</t>
+  </si>
+  <si>
+    <t>Mobiliario-sillón_oficina-1</t>
+  </si>
+  <si>
+    <t>Mobiliario-silla_oficina-2</t>
+  </si>
+  <si>
+    <t>Mobiliario-silla_oficina-1</t>
+  </si>
+  <si>
+    <t>Impresora-hp_laserjet_pro_mfp479fdw</t>
+  </si>
+  <si>
+    <t>Impresora-hp_laserjet_1022</t>
+  </si>
+  <si>
+    <t>Impresora-ricoh_aficio4310n</t>
+  </si>
+  <si>
+    <t>Impresora-ricoh_aficio_spC430dn</t>
+  </si>
+  <si>
+    <t>Impresora-ricoh_aficio_mp_c300</t>
+  </si>
+  <si>
+    <t>Notebook-elitebook_840G3-3</t>
+  </si>
+  <si>
+    <t>Notebook-elitebook_840G3-2</t>
+  </si>
+  <si>
+    <t>Notebook-elitebook_840G3-1</t>
+  </si>
+  <si>
+    <t>Notebook-hp_elitebook_8470p</t>
+  </si>
+  <si>
+    <t>Notebook-hp_elitebook_8440p-2</t>
+  </si>
+  <si>
+    <t>Notebook-hp_elitebook_8440p-1</t>
+  </si>
+  <si>
+    <t>Notebook-hp_elitebook_6930p</t>
+  </si>
+  <si>
+    <t>Pc-hp_compaq_dc5200</t>
+  </si>
+  <si>
+    <t>Pc-lenovo_thinkcentre</t>
+  </si>
+  <si>
+    <t>Pc-hp_compaq_6300pro-1</t>
+  </si>
+  <si>
+    <t>Pc-hp_compaq_6300pro-3</t>
+  </si>
+  <si>
+    <t>Pc-hp_compaq_6300pro-2</t>
+  </si>
+  <si>
+    <t>Pc-hp_proDesk_400</t>
   </si>
 </sst>
 </file>
@@ -696,88 +696,88 @@
         <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
